--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2.453123336121546</v>
+        <v>0.3986325421197512</v>
       </c>
       <c r="D2" t="n">
-        <v>2.246332652861294</v>
+        <v>0.3650290560899603</v>
       </c>
       <c r="E2" t="n">
-        <v>10.85646177663179</v>
+        <v>1.764175038702666</v>
       </c>
       <c r="F2" t="n">
-        <v>10.8866783497521</v>
+        <v>1.769085231834715</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9078568765124549</v>
+        <v>0.1475267424332739</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9143418775516587</v>
+        <v>0.1485805551021445</v>
       </c>
       <c r="E3" t="n">
-        <v>10.85646177663179</v>
+        <v>1.764175038702666</v>
       </c>
       <c r="F3" t="n">
-        <v>10.8866783497521</v>
+        <v>1.769085231834715</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.67160891467879</v>
+        <v>4.009136448635303</v>
       </c>
       <c r="D4" t="n">
-        <v>24.6456422738161</v>
+        <v>4.004916869495116</v>
       </c>
       <c r="E4" t="n">
-        <v>10.85646177663179</v>
+        <v>1.764175038702666</v>
       </c>
       <c r="F4" t="n">
-        <v>10.8866783497521</v>
+        <v>1.769085231834715</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
